--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2327-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2327-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0467BA31-98B4-4F1C-AFC8-47CC865A77E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DCB07CE-9BA2-4FE0-801B-F6B2596B75EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{917F1A02-A345-4AFA-A714-7EB10EC8B0C6}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{A02CABD6-1E2F-4F92-B236-E53D4F39220C}"/>
   </bookViews>
   <sheets>
     <sheet name="2327-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1526,21 +1526,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C72F4B6-1395-4DF9-83BB-470569216A4E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94332153-E0EC-4B2B-80D0-6F4BE1F7B2AB}">
   <dimension ref="A1:R63"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="14.125" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="10" width="9.75" customWidth="1"/>
+    <col min="11" max="13" width="9.25" customWidth="1"/>
+    <col min="14" max="14" width="9.75" customWidth="1"/>
+    <col min="15" max="17" width="9.25" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1568,7 +1568,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1598,7 +1598,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1644,7 +1644,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1694,7 +1694,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="41">
         <v>2025</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="39">
         <v>2024</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="43" t="s">
         <v>26</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="44"/>
       <c r="B14" s="22" t="s">
         <v>32</v>
@@ -2214,7 +2214,7 @@
       <c r="Q14" s="48"/>
       <c r="R14" s="48"/>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="41">
         <v>2023</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>26</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>26</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>26</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2022</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>26</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2714,7 +2714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="41">
         <v>2021</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>26</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>26</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="39">
         <v>2020</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>26</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="41">
         <v>2019</v>
       </c>
@@ -3100,7 +3100,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>26</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>26</v>
       </c>
@@ -3212,7 +3212,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="39">
         <v>2018</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="41">
         <v>2017</v>
       </c>
@@ -3320,7 +3320,7 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="39">
         <v>2016</v>
       </c>
@@ -3374,7 +3374,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="41">
         <v>2015</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="39">
         <v>2014</v>
       </c>
@@ -3482,7 +3482,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="41">
         <v>2013</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="39">
         <v>2012</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="41">
         <v>2011</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="39">
         <v>2010</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="41">
         <v>2009</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="39">
         <v>2008</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="41">
         <v>2007</v>
       </c>
@@ -3860,7 +3860,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="39">
         <v>2006</v>
       </c>
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="41">
         <v>2005</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="39">
         <v>2004</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="41">
         <v>2003</v>
       </c>
@@ -4076,7 +4076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="39">
         <v>2002</v>
       </c>
@@ -4130,7 +4130,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="41">
         <v>2001</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>9.31</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="39">
         <v>2000</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>3.07</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="41">
         <v>1999</v>
       </c>
@@ -4292,7 +4292,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="39">
         <v>1998</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="41">
         <v>1997</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="39">
         <v>1996</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>7.84</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="41">
         <v>1995</v>
       </c>
@@ -4508,7 +4508,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="39">
         <v>1994</v>
       </c>
@@ -4562,7 +4562,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="41">
         <v>1993</v>
       </c>
@@ -4616,7 +4616,7 @@
         <v>8.65</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="39">
         <v>1991</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="41">
         <v>1990</v>
       </c>
@@ -4724,7 +4724,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="39">
         <v>1988</v>
       </c>
@@ -4778,7 +4778,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="41">
         <v>1987</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="39" t="s">
         <v>48</v>
       </c>
